--- a/data/Wohlen (AG)/investment_decision/Wohlen AG_district_investment_decision.xlsx
+++ b/data/Wohlen (AG)/investment_decision/Wohlen AG_district_investment_decision.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,32 +461,32 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>scen_all_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_all_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_dr_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_candidate_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>70.79855525050566</v>
+        <v>21.2965012652299</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -524,7 +524,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>21.2965012652299</v>
+        <v>70.79855525050566</v>
       </c>
     </row>
     <row r="3">
@@ -549,7 +549,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>70.79855525050566</v>
+        <v>33.78047846526391</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -561,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>33.78047846526391</v>
+        <v>70.79855525050566</v>
       </c>
     </row>
     <row r="4">
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>70.79855525050566</v>
+        <v>41.69324791256537</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -598,7 +598,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>41.69324791256537</v>
+        <v>70.79855525050566</v>
       </c>
     </row>
     <row r="5">
@@ -623,7 +623,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>70.79855525050566</v>
+        <v>47.01567160913866</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -635,7 +635,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>47.01567160913866</v>
+        <v>70.79855525050566</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>70.79855525050566</v>
+        <v>50.7699915179476</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>50.7699915179476</v>
+        <v>70.79855525050566</v>
       </c>
     </row>
     <row r="7">
@@ -680,7 +680,7 @@
         <v>46023</v>
       </c>
       <c r="B7" t="n">
-        <v>2.329163275308432</v>
+        <v>2.721804261152941</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -694,22 +694,22 @@
         <v>70.79855525050566</v>
       </c>
       <c r="F7" t="n">
-        <v>2.329163275308433</v>
+        <v>2.721804261152941</v>
       </c>
       <c r="G7" t="n">
-        <v>70.79855525050566</v>
+        <v>21.2965012652299</v>
       </c>
       <c r="H7" t="n">
-        <v>2.329163275308433</v>
+        <v>2.723308093921989</v>
       </c>
       <c r="I7" t="n">
         <v>21.2965012652299</v>
       </c>
       <c r="J7" t="n">
-        <v>2.329163275308433</v>
+        <v>2.721804261152941</v>
       </c>
       <c r="K7" t="n">
-        <v>21.2965012652299</v>
+        <v>70.79855525050566</v>
       </c>
     </row>
     <row r="8">
@@ -717,7 +717,7 @@
         <v>47849</v>
       </c>
       <c r="B8" t="n">
-        <v>2.329163275308432</v>
+        <v>2.79277707416557</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -731,22 +731,22 @@
         <v>70.79855525050566</v>
       </c>
       <c r="F8" t="n">
-        <v>2.329163275308433</v>
+        <v>2.807776921814617</v>
       </c>
       <c r="G8" t="n">
-        <v>70.79855525050566</v>
+        <v>33.78047846526391</v>
       </c>
       <c r="H8" t="n">
-        <v>2.329163275308433</v>
+        <v>2.798741565537553</v>
       </c>
       <c r="I8" t="n">
         <v>33.78047846526391</v>
       </c>
       <c r="J8" t="n">
-        <v>2.329163275308433</v>
+        <v>2.807776921814617</v>
       </c>
       <c r="K8" t="n">
-        <v>33.78047846526391</v>
+        <v>70.79855525050566</v>
       </c>
     </row>
     <row r="9">
@@ -754,7 +754,7 @@
         <v>49675</v>
       </c>
       <c r="B9" t="n">
-        <v>2.37738032482279</v>
+        <v>3.553325703792167</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -768,22 +768,22 @@
         <v>70.79855525050566</v>
       </c>
       <c r="F9" t="n">
-        <v>2.373739346774525</v>
+        <v>3.576246864785098</v>
       </c>
       <c r="G9" t="n">
-        <v>70.79855525050566</v>
+        <v>41.69324791256537</v>
       </c>
       <c r="H9" t="n">
-        <v>2.374915008657814</v>
+        <v>3.552997369624991</v>
       </c>
       <c r="I9" t="n">
         <v>41.69324791256537</v>
       </c>
       <c r="J9" t="n">
-        <v>2.380655337456054</v>
+        <v>3.582735802597228</v>
       </c>
       <c r="K9" t="n">
-        <v>41.69324791256537</v>
+        <v>70.79855525050566</v>
       </c>
     </row>
     <row r="10">
@@ -791,7 +791,7 @@
         <v>51502</v>
       </c>
       <c r="B10" t="n">
-        <v>2.429569677621612</v>
+        <v>3.695400218495805</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -805,22 +805,22 @@
         <v>70.79855525050566</v>
       </c>
       <c r="F10" t="n">
-        <v>2.409536130328776</v>
+        <v>3.693013063793864</v>
       </c>
       <c r="G10" t="n">
-        <v>70.79855525050566</v>
+        <v>47.01567160913866</v>
       </c>
       <c r="H10" t="n">
-        <v>2.409536130328776</v>
+        <v>3.693655187555292</v>
       </c>
       <c r="I10" t="n">
         <v>47.01567160913866</v>
       </c>
       <c r="J10" t="n">
-        <v>2.429569677621612</v>
+        <v>3.704069888195999</v>
       </c>
       <c r="K10" t="n">
-        <v>47.01567160913866</v>
+        <v>70.79855525050566</v>
       </c>
     </row>
     <row r="11">
@@ -828,7 +828,7 @@
         <v>53328</v>
       </c>
       <c r="B11" t="n">
-        <v>2.429569677621612</v>
+        <v>3.668300912463733</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -842,22 +842,22 @@
         <v>70.79855525050566</v>
       </c>
       <c r="F11" t="n">
-        <v>2.409536130328776</v>
+        <v>3.664666313982414</v>
       </c>
       <c r="G11" t="n">
-        <v>70.79855525050566</v>
+        <v>50.7699915179476</v>
       </c>
       <c r="H11" t="n">
-        <v>2.409536130328776</v>
+        <v>3.663933794920796</v>
       </c>
       <c r="I11" t="n">
         <v>50.7699915179476</v>
       </c>
       <c r="J11" t="n">
-        <v>2.429569677621612</v>
+        <v>3.670585990688961</v>
       </c>
       <c r="K11" t="n">
-        <v>50.7699915179476</v>
+        <v>70.79855525050566</v>
       </c>
     </row>
     <row r="12">
@@ -1043,746 +1043,6 @@
       </c>
       <c r="K16" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0.09782621075292376</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Wohlen AG</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>175</v>
-      </c>
-      <c r="E17" t="n">
-        <v>47.70829960296584</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.0978262107529233</v>
-      </c>
-      <c r="G17" t="n">
-        <v>47.70829960296584</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.09782621075292397</v>
-      </c>
-      <c r="I17" t="n">
-        <v>47.70829960296584</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.09782621075292335</v>
-      </c>
-      <c r="K17" t="n">
-        <v>47.70829960296584</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0.0978262107529233</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Wohlen AG</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>175</v>
-      </c>
-      <c r="E18" t="n">
-        <v>47.70829960296584</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.09782621075292332</v>
-      </c>
-      <c r="G18" t="n">
-        <v>47.70829960296584</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.09782621075292397</v>
-      </c>
-      <c r="I18" t="n">
-        <v>47.70829960296584</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.09782621075292335</v>
-      </c>
-      <c r="K18" t="n">
-        <v>47.70829960296584</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.1000304187307225</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Wohlen AG</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>175</v>
-      </c>
-      <c r="E19" t="n">
-        <v>47.70829960296584</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.0998639740199451</v>
-      </c>
-      <c r="G19" t="n">
-        <v>47.70829960296584</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.09991771856318073</v>
-      </c>
-      <c r="I19" t="n">
-        <v>47.70829960296584</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.1001801335939544</v>
-      </c>
-      <c r="K19" t="n">
-        <v>47.70829960296584</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.104206363385257</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Wohlen AG</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>175</v>
-      </c>
-      <c r="E20" t="n">
-        <v>47.70829960296584</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.1052897534893631</v>
-      </c>
-      <c r="G20" t="n">
-        <v>47.70829960296584</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.1053018067830971</v>
-      </c>
-      <c r="I20" t="n">
-        <v>47.70829960296584</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.1048399565278758</v>
-      </c>
-      <c r="K20" t="n">
-        <v>47.70829960296584</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0.1057340590222985</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Wohlen AG</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>175</v>
-      </c>
-      <c r="E21" t="n">
-        <v>47.70829960296584</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.1068240713211984</v>
-      </c>
-      <c r="G21" t="n">
-        <v>47.70829960296584</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.1065022630653391</v>
-      </c>
-      <c r="I21" t="n">
-        <v>47.70829960296584</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.1062499204427423</v>
-      </c>
-      <c r="K21" t="n">
-        <v>47.70829960296584</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Wohlen AG</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>8</v>
-      </c>
-      <c r="E22" t="n">
-        <v>7.8346983412603</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>7.8346983412603</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.2450839136151787</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.2450839136151787</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Wohlen AG</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E23" t="n">
-        <v>7.8346983412603</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>7.8346983412603</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.457231476396162</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.457231476396162</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Wohlen AG</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>8</v>
-      </c>
-      <c r="E24" t="n">
-        <v>7.8346983412603</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>7.8346983412603</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.643873739233578</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.643873739233578</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Wohlen AG</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>8</v>
-      </c>
-      <c r="E25" t="n">
-        <v>7.8346983412603</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>7.8346983412603</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.8103214875913449</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.8103214875913449</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Wohlen AG</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>8</v>
-      </c>
-      <c r="E26" t="n">
-        <v>7.8346983412603</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>7.8346983412603</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.9604088068369191</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.9604088068369191</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Wohlen AG</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E27" t="n">
-        <v>15.10303294700781</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>15.10303294700781</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.4724509178123927</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.4724509178123927</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Wohlen AG</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E28" t="n">
-        <v>15.10303294700781</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>15.10303294700781</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.8814100749805531</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.8814100749805531</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Wohlen AG</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E29" t="n">
-        <v>15.10303294700781</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>15.10303294700781</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1.241202388884006</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1.241202388884006</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Wohlen AG</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E30" t="n">
-        <v>15.10303294700781</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>15.10303294700781</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1.562065518248376</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>1.562065518248376</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Wohlen AG</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E31" t="n">
-        <v>15.10303294700781</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>15.10303294700781</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1.851390471010928</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1.851390471010928</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Wohlen AG</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>300</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.2089252891002747</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.2089252891002747</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.0065355710297381</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.0065355710297381</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Wohlen AG</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>300</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.2089252891002747</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.2089252891002747</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.01219283937056432</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.01219283937056432</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Wohlen AG</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>300</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.2089252891002747</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.2089252891002747</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.01716996637956208</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.01716996637956208</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Wohlen AG</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>300</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.2089252891002747</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.2089252891002747</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.02160857300243587</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.02160857300243587</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Wohlen AG</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>300</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.2089252891002747</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.2089252891002747</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.02561090151565118</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.02561090151565118</v>
       </c>
     </row>
   </sheetData>
